--- a/deliverables/kpi_workbook.xlsx
+++ b/deliverables/kpi_workbook.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecasts" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reorder list" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spend" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leakage drill-down" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3149,4 +3150,653 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>sales_rep</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>leakage_eur</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>excess_eur</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>within_policy_eur</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>leakage_pct_of_revenue</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>orders</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>orders_above_policy_pct</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>median_discount_pct</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>p90_discount_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Nordics</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>268809.88</v>
+      </c>
+      <c r="D2" t="n">
+        <v>75779.12</v>
+      </c>
+      <c r="E2" t="n">
+        <v>193030.77</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12.46</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1256</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="I2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J2" t="n">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Nowak</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>292291.68</v>
+      </c>
+      <c r="D3" t="n">
+        <v>73367.53999999999</v>
+      </c>
+      <c r="E3" t="n">
+        <v>218924.14</v>
+      </c>
+      <c r="F3" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1705</v>
+      </c>
+      <c r="H3" t="n">
+        <v>28.68</v>
+      </c>
+      <c r="I3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>255726.32</v>
+      </c>
+      <c r="D4" t="n">
+        <v>67365.46000000001</v>
+      </c>
+      <c r="E4" t="n">
+        <v>188360.86</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1319</v>
+      </c>
+      <c r="H4" t="n">
+        <v>35.41</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Braun</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DACH-North</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>193020.03</v>
+      </c>
+      <c r="D5" t="n">
+        <v>61165.41</v>
+      </c>
+      <c r="E5" t="n">
+        <v>131854.61</v>
+      </c>
+      <c r="F5" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="I5" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Lindqvist</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Nordics</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>227292.66</v>
+      </c>
+      <c r="D6" t="n">
+        <v>58971.41</v>
+      </c>
+      <c r="E6" t="n">
+        <v>168321.26</v>
+      </c>
+      <c r="F6" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1320</v>
+      </c>
+      <c r="H6" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="I6" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="J6" t="n">
+        <v>15.41</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Huber</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DACH-South</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>226439.2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>57778.63</v>
+      </c>
+      <c r="E7" t="n">
+        <v>168660.57</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1238</v>
+      </c>
+      <c r="H7" t="n">
+        <v>29.81</v>
+      </c>
+      <c r="I7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Kovac</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>230501.81</v>
+      </c>
+      <c r="D8" t="n">
+        <v>56835.43</v>
+      </c>
+      <c r="E8" t="n">
+        <v>173666.39</v>
+      </c>
+      <c r="F8" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1618</v>
+      </c>
+      <c r="H8" t="n">
+        <v>31.95</v>
+      </c>
+      <c r="I8" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="J8" t="n">
+        <v>14.93</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Fischer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DACH-South</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>211609.99</v>
+      </c>
+      <c r="D9" t="n">
+        <v>56449.13</v>
+      </c>
+      <c r="E9" t="n">
+        <v>155160.86</v>
+      </c>
+      <c r="F9" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1211</v>
+      </c>
+      <c r="H9" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Dubois</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>209606.69</v>
+      </c>
+      <c r="D10" t="n">
+        <v>50626.49</v>
+      </c>
+      <c r="E10" t="n">
+        <v>158980.2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1260</v>
+      </c>
+      <c r="H10" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Weber</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DACH-North</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>183968.93</v>
+      </c>
+      <c r="D11" t="n">
+        <v>47920.45</v>
+      </c>
+      <c r="E11" t="n">
+        <v>136048.49</v>
+      </c>
+      <c r="F11" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1031</v>
+      </c>
+      <c r="H11" t="n">
+        <v>37.54</v>
+      </c>
+      <c r="I11" t="n">
+        <v>8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Mayer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DACH-South</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>177868.8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>40980.51</v>
+      </c>
+      <c r="E12" t="n">
+        <v>136888.29</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1282</v>
+      </c>
+      <c r="H12" t="n">
+        <v>28.86</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>14.89</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Klein</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DACH-North</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>137766.64</v>
+      </c>
+      <c r="D13" t="n">
+        <v>33485.41</v>
+      </c>
+      <c r="E13" t="n">
+        <v>104281.23</v>
+      </c>
+      <c r="F13" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="G13" t="n">
+        <v>972</v>
+      </c>
+      <c r="H13" t="n">
+        <v>32</v>
+      </c>
+      <c r="I13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>By region</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>leakage_eur</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>excess_eur</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>leakage_pct_of_revenue</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>orders_above_policy_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DACH-South</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>615917.99</v>
+      </c>
+      <c r="C17" t="n">
+        <v>155208.28</v>
+      </c>
+      <c r="D17" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="E17" t="n">
+        <v>29.54</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>DACH-North</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>514755.59</v>
+      </c>
+      <c r="C18" t="n">
+        <v>142571.27</v>
+      </c>
+      <c r="D18" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="E18" t="n">
+        <v>35.94</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Nordics</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>496102.54</v>
+      </c>
+      <c r="C19" t="n">
+        <v>134750.52</v>
+      </c>
+      <c r="D19" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="E19" t="n">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>522793.49</v>
+      </c>
+      <c r="C20" t="n">
+        <v>130202.97</v>
+      </c>
+      <c r="D20" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="E20" t="n">
+        <v>30.27</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>465333</v>
+      </c>
+      <c r="C21" t="n">
+        <v>117991.95</v>
+      </c>
+      <c r="D21" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="E21" t="n">
+        <v>32.57</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Policy threshold %</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>assumed sanctioned-discount ceiling (no contract terms in the dataset); within-policy vs excess split depends on it, the total leakage does not</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/deliverables/kpi_workbook.xlsx
+++ b/deliverables/kpi_workbook.xlsx
@@ -13,8 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFM top" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecasts" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reorder list" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spend" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leakage drill-down" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue bridge" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spend" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leakage drill-down" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2984,167 +2985,335 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>channel</t>
+          <t>product_category</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>cogs_eur</t>
+          <t>prior_units</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>returns_cost_eur</t>
+          <t>current_units</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>discount_leakage_eur</t>
+          <t>prior_price_eur</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>cost_to_serve_eur</t>
+          <t>current_price_eur</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>orders</t>
+          <t>prior_revenue_eur</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>current_revenue_eur</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>price_effect_eur</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>volume_effect_eur</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>mix_effect_eur</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>e-shop</t>
+          <t>power tools</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7020516.84</v>
+        <v>63916</v>
       </c>
       <c r="C2" t="n">
-        <v>244100.49</v>
+        <v>66909</v>
       </c>
       <c r="D2" t="n">
-        <v>1044013.27</v>
+        <v>128.4457</v>
       </c>
       <c r="E2" t="n">
-        <v>8308630.6</v>
+        <v>128.7716</v>
       </c>
       <c r="F2" t="n">
-        <v>6011</v>
+        <v>8209735.59</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8615979.77</v>
+      </c>
+      <c r="H2" t="n">
+        <v>21806.19</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1074581.97</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-690143.98</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>field-sales</t>
+          <t>hand tools</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4997452.2</v>
+        <v>59940</v>
       </c>
       <c r="C3" t="n">
-        <v>186012.07</v>
+        <v>66309</v>
       </c>
       <c r="D3" t="n">
-        <v>786435.41</v>
+        <v>21.9601</v>
       </c>
       <c r="E3" t="n">
-        <v>5969899.68</v>
+        <v>21.9668</v>
       </c>
       <c r="F3" t="n">
-        <v>4621</v>
+        <v>1316286.22</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1456599.09</v>
+      </c>
+      <c r="H3" t="n">
+        <v>449.22</v>
+      </c>
+      <c r="I3" t="n">
+        <v>172290.26</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-32426.61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>branch</t>
+          <t>chemicals</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3276233.28</v>
+        <v>88469</v>
       </c>
       <c r="C4" t="n">
-        <v>105170.91</v>
+        <v>107194</v>
       </c>
       <c r="D4" t="n">
-        <v>523318.1</v>
+        <v>5.9495</v>
       </c>
       <c r="E4" t="n">
-        <v>3904722.29</v>
+        <v>5.9224</v>
       </c>
       <c r="F4" t="n">
-        <v>3084</v>
+        <v>526343.62</v>
+      </c>
+      <c r="G4" t="n">
+        <v>634846.49</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-2900.95</v>
+      </c>
+      <c r="I4" t="n">
+        <v>68893.74000000001</v>
+      </c>
+      <c r="J4" t="n">
+        <v>42510.08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>ppe</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1740474.62</v>
+        <v>90744</v>
       </c>
       <c r="C5" t="n">
-        <v>49860.37</v>
+        <v>104792</v>
       </c>
       <c r="D5" t="n">
-        <v>261135.85</v>
+        <v>3.1424</v>
       </c>
       <c r="E5" t="n">
-        <v>2051470.84</v>
+        <v>3.1102</v>
       </c>
       <c r="F5" t="n">
-        <v>1501</v>
+        <v>285150.32</v>
+      </c>
+      <c r="G5" t="n">
+        <v>325919.53</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-3374.66</v>
+      </c>
+      <c r="I5" t="n">
+        <v>37323.66</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6820.21</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>fasteners</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>151866</v>
+      </c>
+      <c r="C6" t="n">
+        <v>169831</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8214</v>
+      </c>
+      <c r="F6" t="n">
+        <v>125287.04</v>
+      </c>
+      <c r="G6" t="n">
+        <v>139497.92</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-609.96</v>
+      </c>
+      <c r="I6" t="n">
+        <v>16398.97</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-1578.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total COGS</t>
+          <t>abrasives</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17034676.94</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Discount leakage EUR</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2614902.63</v>
+        <v>93215</v>
+      </c>
+      <c r="C7" t="n">
+        <v>104863</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.0035</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F7" t="n">
+        <v>93540.58</v>
+      </c>
+      <c r="G7" t="n">
+        <v>105907.67</v>
+      </c>
+      <c r="H7" t="n">
+        <v>678.41</v>
+      </c>
+      <c r="I7" t="n">
+        <v>12243.64</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-554.95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Discount leakage %</t>
+          <t>Prior revenue EUR</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10.69</v>
+        <v>10556343.37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Returns cost total</t>
+          <t>Current revenue EUR</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>585472.5699999999</v>
+        <v>11278750.47</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Total change EUR</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>722407.1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Price effect EUR</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>16048.25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Volume effect EUR</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1381732.23</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Mix effect EUR</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-675373.38</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>price+volume+mix = total change (mix is the residual); synthetic data</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3158,6 +3327,180 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>channel</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>cogs_eur</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>returns_cost_eur</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>discount_leakage_eur</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>cost_to_serve_eur</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>orders</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>e-shop</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>7020516.84</v>
+      </c>
+      <c r="C2" t="n">
+        <v>244100.49</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1044013.27</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8308630.6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>6011</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>field-sales</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4997452.2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>186012.07</v>
+      </c>
+      <c r="D3" t="n">
+        <v>786435.41</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5969899.68</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4621</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>branch</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3276233.28</v>
+      </c>
+      <c r="C4" t="n">
+        <v>105170.91</v>
+      </c>
+      <c r="D4" t="n">
+        <v>523318.1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3904722.29</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3084</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1740474.62</v>
+      </c>
+      <c r="C5" t="n">
+        <v>49860.37</v>
+      </c>
+      <c r="D5" t="n">
+        <v>261135.85</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2051470.84</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Total COGS</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>17034676.94</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Discount leakage EUR</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2614902.63</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Discount leakage %</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>10.69</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Returns cost total</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>585472.5699999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/deliverables/kpi_workbook.xlsx
+++ b/deliverables/kpi_workbook.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue bridge" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spend" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leakage drill-down" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI exceptions" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -591,6 +592,480 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>lower_limit</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>upper_limit</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>modified_z</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>direction</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>favorable</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>OTIF %</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>79.04000000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>86.45999999999999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>82.18000000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>90.73999999999999</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-6.066</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>below</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>severe</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>OTIF %</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>86.45999999999999</v>
+      </c>
+      <c r="E3" t="n">
+        <v>82.18000000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>90.73999999999999</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-5.036</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>below</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>elevated</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>OTIF %</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>80.45999999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>86.45999999999999</v>
+      </c>
+      <c r="E4" t="n">
+        <v>82.18000000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>90.73999999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-4.905</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>below</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>elevated</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>OTIF %</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>81.01000000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>86.45999999999999</v>
+      </c>
+      <c r="E5" t="n">
+        <v>82.18000000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>90.73999999999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-4.456</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>below</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>elevated</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>OTIF %</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>81.52</v>
+      </c>
+      <c r="D6" t="n">
+        <v>86.45999999999999</v>
+      </c>
+      <c r="E6" t="n">
+        <v>82.18000000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>90.73999999999999</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-4.039</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>below</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>elevated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>OTIF %</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>81.78</v>
+      </c>
+      <c r="D7" t="n">
+        <v>86.45999999999999</v>
+      </c>
+      <c r="E7" t="n">
+        <v>82.18000000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>90.73999999999999</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-3.826</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>below</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>elevated</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Control limits (median +/- k*MAD/0.6745), k =</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>centre</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>lower_limit</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>upper_limit</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>months_flagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="C11" t="n">
+        <v>19.11</v>
+      </c>
+      <c r="D11" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>OTIF %</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>86.45999999999999</v>
+      </c>
+      <c r="C12" t="n">
+        <v>82.18000000000001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>90.73999999999999</v>
+      </c>
+      <c r="E12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Returns rate %</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Discount leakage %</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="C14" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Average order value</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1458.86</v>
+      </c>
+      <c r="C15" t="n">
+        <v>852.6799999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2065.04</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>robust control chart (median ± k·MAD/0.6745, Iglewicz–Hoaglin modified z)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Volume series (revenue, orders) excluded from level-anomaly detection on 24 points; see forecast CV + revenue bridge. Synthetic data.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/deliverables/kpi_workbook.xlsx
+++ b/deliverables/kpi_workbook.xlsx
@@ -17,6 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spend" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leakage drill-down" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI exceptions" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pacing to plan" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1066,6 +1067,323 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sales pacing &amp; target attainment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Fiscal year</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>As of</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Months elapsed / remaining</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>9 / 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>YTD actual EUR</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>8252457.12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Plan-to-date (seasonalized) EUR</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>8528901.09</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Pace index (YTD / plan-to-date)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.9676</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Annual plan EUR</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>11400850.84</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Plan is assumed?</t>
+        </is>
+      </c>
+      <c r="B10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Plan growth % (if assumed)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Prior-FY revenue EUR</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>10556343.37</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Projection model</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>seasonal_naive</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Projection CV-MASE</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.2127</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Projected remaining EUR</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2659212.73</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Projected full-year EUR</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>10911669.85</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Simple annualise-YTD run-rate EUR</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>11003276.16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>80% interval low EUR</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>10769898.75</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>80% interval high EUR</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>11053440.95</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Backtest folds</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Backtest error sigma EUR/mo</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>63869.13</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Projected attainment %</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>95.70999999999999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Attainment low–high %</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>94.47–96.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Gap to plan EUR</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>-489180.99</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>behind plan — at risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Realised full-year EUR</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>11278750.47</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Realised attainment %</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>98.93000000000001</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Realised within interval?</t>
+        </is>
+      </c>
+      <c r="B28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>assumed plan = prior-FY revenue x (1 + 8.0%); the dataset carries no budget, so every attainment figure moves with this rate (a stated assumption, not a measured target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Projection is out-of-sample (rolling-origin-CV-selected model); the interval is an empirical, normal-approx band aggregated over the remaining months (independence assumption). Modelled, not a guarantee. Synthetic data.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
